--- a/back_end/data/warehouse/고려.xlsx
+++ b/back_end/data/warehouse/고려.xlsx
@@ -23,7 +23,7 @@
     <t>조회기간 :</t>
   </si>
   <si>
-    <t>2026-05-29 ~ 2026-05-29</t>
+    <t>2026-06-05 ~ 2026-06-05</t>
   </si>
   <si>
     <t>♠통관 잔여량 : 한 B/L에 여러 개의 수탁품 또는 CSMS에서 통관처리가 안된 경우 등 실제 통관수량과 차이가 있을 수 있습니다.</t>
@@ -136,7 +136,7 @@
     <t>1/1</t>
   </si>
   <si>
-    <t>2026-05-29 09:26:31</t>
+    <t>2026-06-05 09:40:06</t>
   </si>
 </sst>
 </file>
@@ -893,7 +893,7 @@
         <v>33</v>
       </c>
       <c r="V6" s="9">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c t="s" r="W6" s="13">
         <v>34</v>
